--- a/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,12 +499,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SaiMat@123</t>
+          <t>AnhDuong@123</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Username hoặc Password không đúng!</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
     </row>
@@ -516,13 +516,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Duong11Anh</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>KhongDung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AnhDuong@123</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>Username hoặc Password không đúng!</t>
         </is>
       </c>
     </row>
@@ -537,110 +541,12 @@
           <t>AnhDuong11</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>KhongDung</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LG06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AnhDuong@123</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LG07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AnhDuong11</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AnhDuong@123</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AnhDuong11</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LG08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Duong11Anh</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AnhDuong@123</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Username hoặc Password không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LG09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SaiMat@123</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Vui lòng điền vào trường này</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LG10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Duong11Anh</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SaiMat@123</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>Username hoặc Password không đúng!</t>
         </is>

--- a/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KhongDung</t>
+          <t>NguyenVanA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KhongDung</t>
+          <t>NguyenVanA@123</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AnhDuong@123</t>
+          <t>Aa1!aaaa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NguyenVanA</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AnhDuong@123</t>
+          <t>Aa1!aaa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -543,10 +543,54 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NguyenVanA@123</t>
+          <t>Aa1!aaaaa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>Username hoặc Password không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LG06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AnhDuong11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Aa1!aaa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Username hoặc Password không đúng!</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LG07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AnhDuong11</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Aa1!aaaaaa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Username hoặc Password không đúng!</t>
         </is>

--- a/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aa1!aaaa</t>
+          <t>AnhDuong@123</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aa1!aaa</t>
+          <t>SaiPass@123</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -538,59 +538,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
+          <t>KhongTonTai123</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aa1!aaaaa</t>
+          <t>AnhDuong@123</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>Username hoặc Password không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LG06</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AnhDuong11</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Aa1!aaa</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Username hoặc Password không đúng!</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LG07</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AnhDuong11</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Aa1!aaaaaa</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
         <is>
           <t>Username hoặc Password không đúng!</t>
         </is>

--- a/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
@@ -498,17 +498,13 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>wronguser</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AnhDuong@123</t>
-        </is>
-      </c>
+          <t>AnhDuong11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Username hoặc Password không đúng!</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
@@ -520,13 +516,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>User123</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AnhDuong@123</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wrongpass</t>
+          <t>AnhDuong@456</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Username hoặc Password không đúng!</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
     </row>

--- a/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
+++ b/Framework_MWC_Testing/data/ai_processed/login/LoginData.xlsx
@@ -456,11 +456,7 @@
           <t>T001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AnhDuong11</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>AnhDuong@123</t>
@@ -468,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
+          <t>Vui lòng điền vào trường này</t>
         </is>
       </c>
     </row>
@@ -478,12 +474,12 @@
           <t>T002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AnhDuong@123</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AnhDuong11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Vui lòng điền vào trường này</t>
@@ -498,13 +494,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AnhDuong11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>AnhDuong12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AnhDuong@123</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vui lòng điền vào trường này</t>
+          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
         </is>
       </c>
     </row>
@@ -516,12 +516,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>User123</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AnhDuong@123</t>
+          <t>AnhDuong123</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AnhDuong@456</t>
+          <t>AnhDuong@123</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tên đăng nhập hoặc mật khẩu không đúng!</t>
+          <t>AnhDuong11</t>
         </is>
       </c>
     </row>
